--- a/6node_spain/output_a.xlsx
+++ b/6node_spain/output_a.xlsx
@@ -489,13 +489,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1.448378918720291</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8069333896388119</v>
+        <v>0.8700077157713119</v>
       </c>
     </row>
     <row r="4">
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3.622506309480824e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.2263192170913441</v>
       </c>
     </row>
     <row r="5">
@@ -533,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.448378918720291</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -545,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006070787794139079</v>
+        <v>0.3797202862854819</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3.622506309480824e-10</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -570,7 +570,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.708905370183168e-06</v>
+        <v>0.1243543495741979</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8069333896388119</v>
+        <v>0.8700077157713119</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.2263192170913441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006070787794139079</v>
+        <v>0.3797202862854819</v>
       </c>
       <c r="F7" t="n">
-        <v>1.708905370183168e-06</v>
+        <v>0.1243543495741979</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/6node_spain/output_a.xlsx
+++ b/6node_spain/output_a.xlsx
@@ -489,13 +489,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.448378918720291</v>
+        <v>1.473962980448705</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8700077157713119</v>
+        <v>0.8700077517613194</v>
       </c>
     </row>
     <row r="4">
@@ -514,10 +514,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.656378759174014</v>
       </c>
       <c r="F4" t="n">
-        <v>3.622506309480824e-10</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0.2263192170913441</v>
@@ -533,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.448378918720291</v>
+        <v>1.473962980448705</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.656378759174014</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -545,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3797202862854819</v>
+        <v>0.3797202509695052</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3.622506309480824e-10</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -570,7 +570,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1243543495741979</v>
+        <v>0.1243543496159273</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8700077157713119</v>
+        <v>0.8700077517613194</v>
       </c>
       <c r="D7" t="n">
         <v>0.2263192170913441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3797202862854819</v>
+        <v>0.3797202509695052</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1243543495741979</v>
+        <v>0.1243543496159273</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/6node_spain/output_a.xlsx
+++ b/6node_spain/output_a.xlsx
@@ -489,13 +489,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.473962980448705</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8700077517613194</v>
+        <v>0.8130081300813008</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.656378759174014</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2263192170913441</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -533,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.473962980448705</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.656378759174014</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -545,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3797202509695052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1243543496159273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8700077517613194</v>
+        <v>0.8130081300813008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2263192170913441</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3797202509695052</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1243543496159273</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/6node_spain/output_a.xlsx
+++ b/6node_spain/output_a.xlsx
@@ -495,7 +495,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8130081300813008</v>
+        <v>2.345878066070536</v>
       </c>
     </row>
     <row r="4">
@@ -583,7 +583,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8130081300813008</v>
+        <v>2.345878066070536</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>

--- a/6node_spain/output_a.xlsx
+++ b/6node_spain/output_a.xlsx
@@ -489,13 +489,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1.773661332135592</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.345878066070536</v>
+        <v>2.345510673319831</v>
       </c>
     </row>
     <row r="4">
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.3087583941660498</v>
       </c>
     </row>
     <row r="5">
@@ -533,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.773661332135592</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -545,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.4694035942956067</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.1839668190910501</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2.345878066070536</v>
+        <v>2.345510673319831</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.3087583941660498</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.4694035942956067</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.1839668190910501</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/6node_spain/output_a.xlsx
+++ b/6node_spain/output_a.xlsx
@@ -489,7 +489,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.773661332135592</v>
+        <v>1.773661284227677</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -533,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.773661332135592</v>
+        <v>1.773661284227677</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -570,7 +570,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1839668190910501</v>
+        <v>0.1839668669989644</v>
       </c>
     </row>
     <row r="7">
@@ -592,7 +592,7 @@
         <v>0.4694035942956067</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1839668190910501</v>
+        <v>0.1839668669989644</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/6node_spain/output_a.xlsx
+++ b/6node_spain/output_a.xlsx
@@ -458,19 +458,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.0002181636648008357</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4.064371929212977e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3.233029264942841e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.092554890546369e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.582521294328548e-06</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.0002181636648008357</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5.669230804807989e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.773661284227677</v>
+        <v>1.368828954250352</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>5.181651926593764e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.345510673319831</v>
+        <v>0.8681733980848008</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>4.064371929212977e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>5.669230804807989e-05</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.003342225635356782</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5.348014375516973e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3087583941660498</v>
+        <v>0.2262366487586565</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3.233029264942841e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>1.773661284227677</v>
+        <v>1.368828954250352</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.003342225635356782</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4.902817725195176e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4694035942956067</v>
+        <v>0.3791951598320455</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +555,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1.092554890546369e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>5.181651926593764e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5.348014375516973e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>4.902817725195176e-06</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1839668669989644</v>
+        <v>0.1238120553059773</v>
       </c>
     </row>
     <row r="7">
@@ -580,19 +580,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1.582521294328548e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>2.345510673319831</v>
+        <v>0.8681733980848008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3087583941660498</v>
+        <v>0.2262366487586565</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4694035942956067</v>
+        <v>0.3791951598320455</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1839668669989644</v>
+        <v>0.1238120553059773</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/6node_spain/output_a.xlsx
+++ b/6node_spain/output_a.xlsx
@@ -458,19 +458,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002181636648008357</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4.064371929212977e-06</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3.233029264942841e-06</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.092554890546369e-05</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.582521294328548e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0002181636648008357</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>5.669230804807989e-05</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.368828954250352</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5.181651926593764e-06</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8681733980848008</v>
+        <v>0.8680882232344881</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.064371929212977e-06</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>5.669230804807989e-05</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003342225635356782</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5.348014375516973e-06</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2262366487586565</v>
+        <v>0.2265489452170459</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.233029264942841e-06</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.368828954250352</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003342225635356782</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4.902817725195176e-06</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3791951598320455</v>
+        <v>0.3805698416405949</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +555,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.092554890546369e-05</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>5.181651926593764e-06</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>5.348014375516973e-06</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>4.902817725195176e-06</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1238120553059773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,19 +580,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.582521294328548e-06</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8681733980848008</v>
+        <v>0.8680882232344881</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2262366487586565</v>
+        <v>0.2265489452170459</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3791951598320455</v>
+        <v>0.3805698416405949</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1238120553059773</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/6node_spain/output_a.xlsx
+++ b/6node_spain/output_a.xlsx
@@ -495,7 +495,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8680882232344881</v>
+        <v>0.8713080059561737</v>
       </c>
     </row>
     <row r="4">
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2265489452170459</v>
+        <v>0.226699491059051</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3805698416405949</v>
+        <v>0.3804774096437295</v>
       </c>
     </row>
     <row r="6">
@@ -583,13 +583,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8680882232344881</v>
+        <v>0.8713080059561737</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2265489452170459</v>
+        <v>0.226699491059051</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3805698416405949</v>
+        <v>0.3804774096437295</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
